--- a/cucumber-for-appian/src/test/resources/testdata/NovatedApp_Regression/07_NovatedApp_Regression.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/NovatedApp_Regression/07_NovatedApp_Regression.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhana\IdeaProjects\NovatedApp\cucumber-for-appian\src\test\resources\testdata\NovatedApp_Regression\"/>
     </mc:Choice>
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="TestData" sheetId="14" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="157">
   <si>
     <t>TC ID</t>
   </si>
@@ -501,6 +501,9 @@
   </si>
   <si>
     <t>Toshihiko Inafune</t>
+  </si>
+  <si>
+    <t>05 Jun 1995</t>
   </si>
 </sst>
 </file>
@@ -961,8 +964,8 @@
   <dimension ref="A1:BG5"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="47" max="47" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" width="10.875"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" width="18.125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:59" s="1" customFormat="1" ht="81" x14ac:dyDescent="0.15">
@@ -1152,13 +1155,13 @@
         <v>51</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="4">
+      <c r="D2" s="4" t="n">
         <f>C2+1</f>
-        <v>1</v>
-      </c>
-      <c r="E2" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <f>D2</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>52</v>
@@ -1388,43 +1391,43 @@
         <v>58</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="AC3" s="3" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="AE3" s="3" t="s">
         <v>62</v>
       </c>
       <c r="AF3" s="3" t="s">
-        <v>63</v>
+        <v>156</v>
       </c>
       <c r="AG3" s="3" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="AI3" s="3" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="AJ3" s="3" t="s">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="AK3" s="3" t="s">
         <v>68</v>
       </c>
       <c r="AL3" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="AM3" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="AN3" s="3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AO3" s="3" t="s">
         <v>99</v>
@@ -1490,13 +1493,13 @@
         <v>51</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="4">
+      <c r="D4" s="4" t="n">
         <f>C4+1</f>
-        <v>1</v>
-      </c>
-      <c r="E4" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <f>D4</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>52</v>
